--- a/data/ent_nagano.xlsx
+++ b/data/ent_nagano.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10727"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10110"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/taro/works/dpc_dashboard/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/taro/works/dpc_dashboard/nagano_hospital_comparison/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDD19124-AC58-DC4E-9390-F50462B6CF80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95D4DC68-313B-5C44-8965-54F6CFB87396}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3480" yWindow="2620" windowWidth="27640" windowHeight="16940" xr2:uid="{1BC98F22-10F9-BD49-B712-C55C8406704B}"/>
+    <workbookView xWindow="2020" yWindow="9140" windowWidth="27640" windowHeight="16940" xr2:uid="{1BC98F22-10F9-BD49-B712-C55C8406704B}"/>
   </bookViews>
   <sheets>
     <sheet name="退院先" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="40">
   <si>
     <t>告示番号</t>
     <phoneticPr fontId="0"/>
@@ -285,6 +285,9 @@
   </si>
   <si>
     <t>R5</t>
+  </si>
+  <si>
+    <t>R6</t>
   </si>
 </sst>
 </file>
@@ -294,7 +297,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -320,6 +323,12 @@
     <font>
       <sz val="9"/>
       <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="ＭＳ ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
     </font>
@@ -437,33 +446,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -481,6 +463,33 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -787,11 +796,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA39C6C1-946F-FD47-96D3-E0FBAEFC08D5}">
-  <dimension ref="A1:BA12"/>
+  <dimension ref="A1:BK12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="2" width="6.3984375" style="11" customWidth="1"/>
-    <col min="3" max="3" width="49.796875" style="11" customWidth="1"/>
+    <col min="1" max="2" width="6.3984375" style="2" customWidth="1"/>
+    <col min="3" max="3" width="49.796875" style="2" customWidth="1"/>
     <col min="4" max="9" width="7.19921875" customWidth="1"/>
     <col min="10" max="10" width="9.19921875" customWidth="1"/>
     <col min="11" max="13" width="6.3984375" customWidth="1"/>
@@ -814,1844 +823,2187 @@
     <col min="53" max="53" width="6.3984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:53" ht="12" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
+    <row r="1" spans="1:63" ht="12" customHeight="1">
+      <c r="A1" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
-      <c r="I1" s="5"/>
-      <c r="J1" s="5"/>
-      <c r="K1" s="5"/>
-      <c r="L1" s="5"/>
-      <c r="M1" s="6"/>
-      <c r="N1" s="4" t="s">
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
+      <c r="I1" s="8"/>
+      <c r="J1" s="8"/>
+      <c r="K1" s="8"/>
+      <c r="L1" s="8"/>
+      <c r="M1" s="9"/>
+      <c r="N1" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="O1" s="5"/>
-      <c r="P1" s="5"/>
-      <c r="Q1" s="5"/>
-      <c r="R1" s="5"/>
-      <c r="S1" s="5"/>
-      <c r="T1" s="5"/>
-      <c r="U1" s="5"/>
-      <c r="V1" s="5"/>
-      <c r="W1" s="6"/>
-      <c r="X1" s="4" t="s">
+      <c r="O1" s="8"/>
+      <c r="P1" s="8"/>
+      <c r="Q1" s="8"/>
+      <c r="R1" s="8"/>
+      <c r="S1" s="8"/>
+      <c r="T1" s="8"/>
+      <c r="U1" s="8"/>
+      <c r="V1" s="8"/>
+      <c r="W1" s="9"/>
+      <c r="X1" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="Y1" s="5"/>
-      <c r="Z1" s="5"/>
-      <c r="AA1" s="5"/>
-      <c r="AB1" s="5"/>
-      <c r="AC1" s="5"/>
-      <c r="AD1" s="5"/>
-      <c r="AE1" s="5"/>
-      <c r="AF1" s="5"/>
-      <c r="AG1" s="6"/>
-      <c r="AH1" s="4" t="s">
+      <c r="Y1" s="8"/>
+      <c r="Z1" s="8"/>
+      <c r="AA1" s="8"/>
+      <c r="AB1" s="8"/>
+      <c r="AC1" s="8"/>
+      <c r="AD1" s="8"/>
+      <c r="AE1" s="8"/>
+      <c r="AF1" s="8"/>
+      <c r="AG1" s="9"/>
+      <c r="AH1" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="AI1" s="5"/>
-      <c r="AJ1" s="5"/>
-      <c r="AK1" s="5"/>
-      <c r="AL1" s="5"/>
-      <c r="AM1" s="5"/>
-      <c r="AN1" s="5"/>
-      <c r="AO1" s="5"/>
-      <c r="AP1" s="5"/>
-      <c r="AQ1" s="6"/>
-      <c r="AR1" s="4" t="s">
+      <c r="AI1" s="8"/>
+      <c r="AJ1" s="8"/>
+      <c r="AK1" s="8"/>
+      <c r="AL1" s="8"/>
+      <c r="AM1" s="8"/>
+      <c r="AN1" s="8"/>
+      <c r="AO1" s="8"/>
+      <c r="AP1" s="8"/>
+      <c r="AQ1" s="9"/>
+      <c r="AR1" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="AS1" s="5"/>
-      <c r="AT1" s="5"/>
-      <c r="AU1" s="5"/>
-      <c r="AV1" s="5"/>
-      <c r="AW1" s="5"/>
-      <c r="AX1" s="5"/>
-      <c r="AY1" s="5"/>
-      <c r="AZ1" s="5"/>
-      <c r="BA1" s="6"/>
+      <c r="AS1" s="8"/>
+      <c r="AT1" s="8"/>
+      <c r="AU1" s="8"/>
+      <c r="AV1" s="8"/>
+      <c r="AW1" s="8"/>
+      <c r="AX1" s="8"/>
+      <c r="AY1" s="8"/>
+      <c r="AZ1" s="8"/>
+      <c r="BA1" s="9"/>
+      <c r="BB1" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="BC1" s="8"/>
+      <c r="BD1" s="8"/>
+      <c r="BE1" s="8"/>
+      <c r="BF1" s="8"/>
+      <c r="BG1" s="8"/>
+      <c r="BH1" s="8"/>
+      <c r="BI1" s="8"/>
+      <c r="BJ1" s="8"/>
+      <c r="BK1" s="9"/>
     </row>
-    <row r="2" spans="1:53" ht="68.25" customHeight="1">
-      <c r="A2" s="7"/>
-      <c r="B2" s="8"/>
-      <c r="C2" s="9"/>
-      <c r="D2" s="10" t="s">
+    <row r="2" spans="1:63" ht="68.25" customHeight="1">
+      <c r="A2" s="11"/>
+      <c r="B2" s="13"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="E2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="10" t="s">
+      <c r="F2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="10" t="s">
+      <c r="G2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="10" t="s">
+      <c r="H2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I2" s="10" t="s">
+      <c r="I2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J2" s="10" t="s">
+      <c r="J2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K2" s="10" t="s">
+      <c r="K2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L2" s="10" t="s">
+      <c r="L2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M2" s="10" t="s">
+      <c r="M2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N2" s="10" t="s">
+      <c r="N2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="O2" s="10" t="s">
+      <c r="O2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="P2" s="10" t="s">
+      <c r="P2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="Q2" s="10" t="s">
+      <c r="Q2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="R2" s="10" t="s">
+      <c r="R2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="S2" s="10" t="s">
+      <c r="S2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="T2" s="10" t="s">
+      <c r="T2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="U2" s="10" t="s">
+      <c r="U2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="V2" s="10" t="s">
+      <c r="V2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="W2" s="10" t="s">
+      <c r="W2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="X2" s="10" t="s">
+      <c r="X2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="Y2" s="10" t="s">
+      <c r="Y2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="Z2" s="10" t="s">
+      <c r="Z2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="AA2" s="10" t="s">
+      <c r="AA2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="AB2" s="10" t="s">
+      <c r="AB2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="AC2" s="10" t="s">
+      <c r="AC2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="AD2" s="10" t="s">
+      <c r="AD2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="AE2" s="10" t="s">
+      <c r="AE2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="AF2" s="10" t="s">
+      <c r="AF2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="AG2" s="10" t="s">
+      <c r="AG2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="AH2" s="10" t="s">
+      <c r="AH2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="AI2" s="10" t="s">
+      <c r="AI2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="AJ2" s="10" t="s">
+      <c r="AJ2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="AK2" s="10" t="s">
+      <c r="AK2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="AL2" s="10" t="s">
+      <c r="AL2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="AM2" s="10" t="s">
+      <c r="AM2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="AN2" s="10" t="s">
+      <c r="AN2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="AO2" s="10" t="s">
+      <c r="AO2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="AP2" s="10" t="s">
+      <c r="AP2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="AQ2" s="10" t="s">
+      <c r="AQ2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="AR2" s="10" t="s">
+      <c r="AR2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="AS2" s="10" t="s">
+      <c r="AS2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="AT2" s="10" t="s">
+      <c r="AT2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="AU2" s="10" t="s">
+      <c r="AU2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="AV2" s="10" t="s">
+      <c r="AV2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="AW2" s="10" t="s">
+      <c r="AW2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="AX2" s="10" t="s">
+      <c r="AX2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="AY2" s="10" t="s">
+      <c r="AY2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="AZ2" s="10" t="s">
+      <c r="AZ2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="BA2" s="10" t="s">
+      <c r="BA2" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="BB2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BC2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="BD2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="BE2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="BF2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="BG2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="BH2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="BI2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="BJ2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="BK2" s="1" t="s">
+        <v>12</v>
+      </c>
     </row>
-    <row r="3" spans="1:53" s="15" customFormat="1">
-      <c r="A3" s="12" t="s">
+    <row r="3" spans="1:63" s="6" customFormat="1">
+      <c r="A3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="C3" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="14">
+      <c r="D3" s="5">
         <v>0.725059993143641</v>
       </c>
-      <c r="E3" s="14">
+      <c r="E3" s="5">
         <v>0.114775454233802</v>
       </c>
-      <c r="F3" s="14">
+      <c r="F3" s="5">
         <v>5.05999314364073E-2</v>
       </c>
-      <c r="G3" s="14">
+      <c r="G3" s="5">
         <v>6.6095303393897797E-2</v>
       </c>
-      <c r="H3" s="14">
+      <c r="H3" s="5">
         <v>4.5937607130613596E-3</v>
       </c>
-      <c r="I3" s="14">
+      <c r="I3" s="5">
         <v>5.5536510113129902E-3</v>
       </c>
-      <c r="J3" s="14">
+      <c r="J3" s="5">
         <v>6.5821049022968797E-3</v>
       </c>
-      <c r="K3" s="14">
+      <c r="K3" s="5">
         <v>2.6602673980116599E-2</v>
       </c>
-      <c r="L3" s="14">
+      <c r="L3" s="5">
         <v>1.37127185464518E-4</v>
       </c>
-      <c r="M3" s="14">
-        <v>0</v>
-      </c>
-      <c r="N3" s="14">
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="5">
         <v>0.75311268715524005</v>
       </c>
-      <c r="O3" s="14">
+      <c r="O3" s="5">
         <v>9.40898345153664E-2</v>
       </c>
-      <c r="P3" s="14">
+      <c r="P3" s="5">
         <v>3.3096926713947997E-2</v>
       </c>
-      <c r="Q3" s="14">
+      <c r="Q3" s="5">
         <v>7.2340425531914901E-2</v>
       </c>
-      <c r="R3" s="14">
+      <c r="R3" s="5">
         <v>7.09219858156028E-3</v>
       </c>
-      <c r="S3" s="14">
+      <c r="S3" s="5">
         <v>4.0189125295508298E-3</v>
       </c>
-      <c r="T3" s="14">
+      <c r="T3" s="5">
         <v>8.6682427107958992E-3</v>
       </c>
-      <c r="U3" s="14">
+      <c r="U3" s="5">
         <v>2.7265563435776199E-2</v>
       </c>
-      <c r="V3" s="14">
+      <c r="V3" s="5">
         <v>3.1520882584712401E-4</v>
       </c>
-      <c r="W3" s="14">
-        <v>0</v>
-      </c>
-      <c r="X3" s="14">
+      <c r="W3" s="5">
+        <v>0</v>
+      </c>
+      <c r="X3" s="5">
         <v>0.74440128914965698</v>
       </c>
-      <c r="Y3" s="14">
+      <c r="Y3" s="5">
         <v>9.1149491777539005E-2</v>
       </c>
-      <c r="Z3" s="14">
+      <c r="Z3" s="5">
         <v>3.9996694488058801E-2</v>
       </c>
-      <c r="AA3" s="14">
+      <c r="AA3" s="5">
         <v>8.0158664573175803E-2</v>
       </c>
-      <c r="AB3" s="14">
+      <c r="AB3" s="5">
         <v>5.3714569043880698E-3</v>
       </c>
-      <c r="AC3" s="14">
+      <c r="AC3" s="5">
         <v>5.2061813073299703E-3</v>
       </c>
-      <c r="AD3" s="14">
+      <c r="AD3" s="5">
         <v>9.6686224278985204E-3</v>
       </c>
-      <c r="AE3" s="14">
+      <c r="AE3" s="5">
         <v>2.3964961573423701E-2</v>
       </c>
-      <c r="AF3" s="14">
-        <v>0</v>
-      </c>
-      <c r="AG3" s="14">
+      <c r="AF3" s="5">
+        <v>0</v>
+      </c>
+      <c r="AG3" s="5">
         <v>8.2637798529047195E-5</v>
       </c>
-      <c r="AH3" s="14">
+      <c r="AH3" s="5">
         <v>0.76268477826608105</v>
       </c>
-      <c r="AI3" s="14">
+      <c r="AI3" s="5">
         <v>8.2620854974031196E-2</v>
       </c>
-      <c r="AJ3" s="14">
+      <c r="AJ3" s="5">
         <v>3.1082700759089098E-2</v>
       </c>
-      <c r="AK3" s="14">
+      <c r="AK3" s="5">
         <v>7.4950059928086302E-2</v>
       </c>
-      <c r="AL3" s="14">
+      <c r="AL3" s="5">
         <v>4.6344386735916896E-3</v>
       </c>
-      <c r="AM3" s="14">
+      <c r="AM3" s="5">
         <v>4.7143427886536197E-3</v>
       </c>
-      <c r="AN3" s="14">
+      <c r="AN3" s="5">
         <v>9.1889732321214501E-3</v>
       </c>
-      <c r="AO3" s="14">
+      <c r="AO3" s="5">
         <v>2.9724330803036401E-2</v>
       </c>
-      <c r="AP3" s="14">
+      <c r="AP3" s="5">
         <v>3.1961646024770301E-4</v>
       </c>
-      <c r="AQ3" s="14">
+      <c r="AQ3" s="5">
         <v>7.9904115061925698E-5</v>
       </c>
-      <c r="AR3" s="14">
-        <v>0.75749398293341097</v>
-      </c>
-      <c r="AS3" s="14">
-        <v>7.8550069287433494E-2</v>
-      </c>
-      <c r="AT3" s="14">
-        <v>3.7925753045000399E-2</v>
-      </c>
-      <c r="AU3" s="14">
-        <v>7.5268032966231496E-2</v>
-      </c>
-      <c r="AV3" s="14">
-        <v>5.4700605353365898E-3</v>
-      </c>
-      <c r="AW3" s="14">
-        <v>5.3241922543942801E-3</v>
-      </c>
-      <c r="AX3" s="14">
-        <v>9.2626358398366308E-3</v>
-      </c>
-      <c r="AY3" s="14">
-        <v>3.0267668295529099E-2</v>
-      </c>
-      <c r="AZ3" s="14">
-        <v>4.3760484282692698E-4</v>
-      </c>
-      <c r="BA3" s="14">
+      <c r="AR3" s="5">
+        <v>0.75764570109636498</v>
+      </c>
+      <c r="AS3" s="5">
+        <v>7.9342181188690103E-2</v>
+      </c>
+      <c r="AT3" s="5">
+        <v>3.7146566647432197E-2</v>
+      </c>
+      <c r="AU3" s="5">
+        <v>7.5591459896133903E-2</v>
+      </c>
+      <c r="AV3" s="5">
+        <v>4.9769186381996497E-3</v>
+      </c>
+      <c r="AW3" s="5">
+        <v>4.2556260819388301E-3</v>
+      </c>
+      <c r="AX3" s="5">
+        <v>8.9440276976341607E-3</v>
+      </c>
+      <c r="AY3" s="5">
+        <v>3.1664743219850001E-2</v>
+      </c>
+      <c r="AZ3" s="5">
+        <v>4.3277553375649201E-4</v>
+      </c>
+      <c r="BA3" s="5">
+        <v>0</v>
+      </c>
+      <c r="BB3" s="5">
+        <v>0.75171797691039</v>
+      </c>
+      <c r="BC3" s="5">
+        <v>7.00934579439252E-2</v>
+      </c>
+      <c r="BD3" s="5">
+        <v>4.97526113249038E-2</v>
+      </c>
+      <c r="BE3" s="5">
+        <v>7.8889499725123699E-2</v>
+      </c>
+      <c r="BF3" s="5">
+        <v>4.8103353490929097E-3</v>
+      </c>
+      <c r="BG3" s="5">
+        <v>5.3600879604178099E-3</v>
+      </c>
+      <c r="BH3" s="5">
+        <v>1.0307861462341901E-2</v>
+      </c>
+      <c r="BI3" s="5">
+        <v>2.8587135788895001E-2</v>
+      </c>
+      <c r="BJ3" s="5">
+        <v>4.8103353490929097E-4</v>
+      </c>
+      <c r="BK3" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:53" s="15" customFormat="1">
-      <c r="A4" s="12" t="s">
+    <row r="4" spans="1:63" s="6" customFormat="1">
+      <c r="A4" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="13" t="s">
+      <c r="C4" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="14">
+      <c r="D4" s="5">
         <v>0.75219791453690499</v>
       </c>
-      <c r="E4" s="14">
+      <c r="E4" s="5">
         <v>9.4970353710897598E-2</v>
       </c>
-      <c r="F4" s="14">
+      <c r="F4" s="5">
         <v>3.7313432835820899E-2</v>
       </c>
-      <c r="G4" s="14">
+      <c r="G4" s="5">
         <v>4.90697198936823E-2</v>
       </c>
-      <c r="H4" s="14">
+      <c r="H4" s="5">
         <v>1.0222858311183801E-2</v>
       </c>
-      <c r="I4" s="14">
+      <c r="I4" s="5">
         <v>8.2805152320588795E-3</v>
       </c>
-      <c r="J4" s="14">
+      <c r="J4" s="5">
         <v>2.0854630954815E-2</v>
       </c>
-      <c r="K4" s="14">
+      <c r="K4" s="5">
         <v>2.6681660192189701E-2</v>
       </c>
-      <c r="L4" s="14">
+      <c r="L4" s="5">
         <v>4.08914332447352E-4</v>
       </c>
-      <c r="M4" s="14">
-        <v>0</v>
-      </c>
-      <c r="N4" s="14">
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="5">
         <v>0.76751983905219601</v>
       </c>
-      <c r="O4" s="14">
+      <c r="O4" s="5">
         <v>8.9415446518386094E-2</v>
       </c>
-      <c r="P4" s="14">
+      <c r="P4" s="5">
         <v>2.6154018106627899E-2</v>
       </c>
-      <c r="Q4" s="14">
+      <c r="Q4" s="5">
         <v>5.1413881748072002E-2</v>
       </c>
-      <c r="R4" s="14">
+      <c r="R4" s="5">
         <v>7.4885436459148297E-3</v>
       </c>
-      <c r="S4" s="14">
+      <c r="S4" s="5">
         <v>8.0473901866547504E-3</v>
       </c>
-      <c r="T4" s="14">
+      <c r="T4" s="5">
         <v>2.28009388621884E-2</v>
       </c>
-      <c r="U4" s="14">
+      <c r="U4" s="5">
         <v>2.66010953392199E-2</v>
       </c>
-      <c r="V4" s="14">
-        <v>0</v>
-      </c>
-      <c r="W4" s="14">
+      <c r="V4" s="5">
+        <v>0</v>
+      </c>
+      <c r="W4" s="5">
         <v>5.5884654073991302E-4</v>
       </c>
-      <c r="X4" s="14">
+      <c r="X4" s="5">
         <v>0.76539026318762005</v>
       </c>
-      <c r="Y4" s="14">
+      <c r="Y4" s="5">
         <v>9.1494408675025396E-2</v>
       </c>
-      <c r="Z4" s="14">
+      <c r="Z4" s="5">
         <v>2.74483226025076E-2</v>
       </c>
-      <c r="AA4" s="14">
+      <c r="AA4" s="5">
         <v>5.0265446741217697E-2</v>
       </c>
-      <c r="AB4" s="14">
+      <c r="AB4" s="5">
         <v>6.5514514853721902E-3</v>
       </c>
-      <c r="AC4" s="14">
+      <c r="AC4" s="5">
         <v>1.0504913588614001E-2</v>
       </c>
-      <c r="AD4" s="14">
+      <c r="AD4" s="5">
         <v>2.11227832373207E-2</v>
       </c>
-      <c r="AE4" s="14">
+      <c r="AE4" s="5">
         <v>2.6996498362137099E-2</v>
       </c>
-      <c r="AF4" s="14">
-        <v>0</v>
-      </c>
-      <c r="AG4" s="14">
+      <c r="AF4" s="5">
+        <v>0</v>
+      </c>
+      <c r="AG4" s="5">
         <v>2.25912120185248E-4</v>
       </c>
-      <c r="AH4" s="14">
+      <c r="AH4" s="5">
         <v>0.75704887218045103</v>
       </c>
-      <c r="AI4" s="14">
+      <c r="AI4" s="5">
         <v>9.0343045112782003E-2</v>
       </c>
-      <c r="AJ4" s="14">
+      <c r="AJ4" s="5">
         <v>2.2556390977443601E-2</v>
       </c>
-      <c r="AK4" s="14">
+      <c r="AK4" s="5">
         <v>5.3806390977443601E-2</v>
       </c>
-      <c r="AL4" s="14">
+      <c r="AL4" s="5">
         <v>9.5159774436090194E-3</v>
       </c>
-      <c r="AM4" s="14">
+      <c r="AM4" s="5">
         <v>1.0220864661654099E-2</v>
       </c>
-      <c r="AN4" s="14">
+      <c r="AN4" s="5">
         <v>2.2438909774436099E-2</v>
       </c>
-      <c r="AO4" s="14">
+      <c r="AO4" s="5">
         <v>3.3247180451127803E-2</v>
       </c>
-      <c r="AP4" s="14">
+      <c r="AP4" s="5">
         <v>4.69924812030075E-4</v>
       </c>
-      <c r="AQ4" s="14">
+      <c r="AQ4" s="5">
         <v>3.5244360902255599E-4</v>
       </c>
-      <c r="AR4" s="14">
-        <v>0.77811982003315205</v>
-      </c>
-      <c r="AS4" s="14">
-        <v>8.2524271844660199E-2</v>
-      </c>
-      <c r="AT4" s="14">
-        <v>2.2969452995500801E-2</v>
-      </c>
-      <c r="AU4" s="14">
-        <v>4.40445181150841E-2</v>
-      </c>
-      <c r="AV4" s="14">
-        <v>9.35354013734312E-3</v>
-      </c>
-      <c r="AW4" s="14">
-        <v>1.43263083116268E-2</v>
-      </c>
-      <c r="AX4" s="14">
-        <v>1.8115084063462E-2</v>
-      </c>
-      <c r="AY4" s="14">
-        <v>3.01918067724367E-2</v>
-      </c>
-      <c r="AZ4" s="14">
-        <v>0</v>
-      </c>
-      <c r="BA4" s="14">
-        <v>3.5519772673454903E-4</v>
+      <c r="AR4" s="5">
+        <v>0.77590673575129498</v>
+      </c>
+      <c r="AS4" s="5">
+        <v>8.2430522845030593E-2</v>
+      </c>
+      <c r="AT4" s="5">
+        <v>2.4729156853509199E-2</v>
+      </c>
+      <c r="AU4" s="5">
+        <v>4.5807819123881301E-2</v>
+      </c>
+      <c r="AV4" s="5">
+        <v>8.4785680640602906E-3</v>
+      </c>
+      <c r="AW4" s="5">
+        <v>1.44842204427697E-2</v>
+      </c>
+      <c r="AX4" s="5">
+        <v>1.7899199246349501E-2</v>
+      </c>
+      <c r="AY4" s="5">
+        <v>2.9910504003768299E-2</v>
+      </c>
+      <c r="AZ4" s="5">
+        <v>0</v>
+      </c>
+      <c r="BA4" s="5">
+        <v>3.53273669335846E-4</v>
+      </c>
+      <c r="BB4" s="5">
+        <v>0.77399770904925502</v>
+      </c>
+      <c r="BC4" s="5">
+        <v>8.0412371134020597E-2</v>
+      </c>
+      <c r="BD4" s="5">
+        <v>2.7376861397479999E-2</v>
+      </c>
+      <c r="BE4" s="5">
+        <v>5.0400916380297797E-2</v>
+      </c>
+      <c r="BF4" s="5">
+        <v>5.1546391752577301E-3</v>
+      </c>
+      <c r="BG4" s="5">
+        <v>1.0652920962199299E-2</v>
+      </c>
+      <c r="BH4" s="5">
+        <v>1.8785796105383699E-2</v>
+      </c>
+      <c r="BI4" s="5">
+        <v>3.31042382588774E-2</v>
+      </c>
+      <c r="BJ4" s="5">
+        <v>1.1454753722795001E-4</v>
+      </c>
+      <c r="BK4" s="5">
+        <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:53" s="15" customFormat="1">
-      <c r="A5" s="12" t="s">
+    <row r="5" spans="1:63" s="6" customFormat="1">
+      <c r="A5" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="12" t="s">
+      <c r="B5" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="13" t="s">
+      <c r="C5" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D5" s="14">
+      <c r="D5" s="5">
         <v>0.83082077051926295</v>
       </c>
-      <c r="E5" s="14">
+      <c r="E5" s="5">
         <v>3.7353433835845898E-2</v>
       </c>
-      <c r="F5" s="14">
+      <c r="F5" s="5">
         <v>5.8626465661641503E-3</v>
       </c>
-      <c r="G5" s="14">
+      <c r="G5" s="5">
         <v>5.9463986599665002E-2</v>
       </c>
-      <c r="H5" s="14">
+      <c r="H5" s="5">
         <v>5.6951423785594601E-3</v>
       </c>
-      <c r="I5" s="14">
+      <c r="I5" s="5">
         <v>1.5075376884422099E-2</v>
       </c>
-      <c r="J5" s="14">
+      <c r="J5" s="5">
         <v>1.75879396984925E-2</v>
       </c>
-      <c r="K5" s="14">
+      <c r="K5" s="5">
         <v>2.7973199329983298E-2</v>
       </c>
-      <c r="L5" s="14">
+      <c r="L5" s="5">
         <v>1.6750418760468999E-4</v>
       </c>
-      <c r="M5" s="14">
-        <v>0</v>
-      </c>
-      <c r="N5" s="14">
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="5">
         <v>0.84967577127136995</v>
       </c>
-      <c r="O5" s="14">
+      <c r="O5" s="5">
         <v>2.6724307329534298E-2</v>
       </c>
-      <c r="P5" s="14">
+      <c r="P5" s="5">
         <v>6.4845745726075897E-3</v>
       </c>
-      <c r="Q5" s="14">
+      <c r="Q5" s="5">
         <v>5.3055610139516603E-2</v>
       </c>
-      <c r="R5" s="14">
+      <c r="R5" s="5">
         <v>5.5020632737276497E-3</v>
       </c>
-      <c r="S5" s="14">
+      <c r="S5" s="5">
         <v>1.37551581843191E-2</v>
       </c>
-      <c r="T5" s="14">
+      <c r="T5" s="5">
         <v>1.29691491452152E-2</v>
       </c>
-      <c r="U5" s="14">
+      <c r="U5" s="5">
         <v>3.1833366083709999E-2</v>
       </c>
-      <c r="V5" s="14">
-        <v>0</v>
-      </c>
-      <c r="W5" s="14">
-        <v>0</v>
-      </c>
-      <c r="X5" s="14">
+      <c r="V5" s="5">
+        <v>0</v>
+      </c>
+      <c r="W5" s="5">
+        <v>0</v>
+      </c>
+      <c r="X5" s="5">
         <v>0.85307405224906696</v>
       </c>
-      <c r="Y5" s="14">
+      <c r="Y5" s="5">
         <v>1.6696130426242399E-2</v>
       </c>
-      <c r="Z5" s="14">
+      <c r="Z5" s="5">
         <v>1.96425063838146E-3</v>
       </c>
-      <c r="AA5" s="14">
+      <c r="AA5" s="5">
         <v>5.1463366725594199E-2</v>
       </c>
-      <c r="AB5" s="14">
+      <c r="AB5" s="5">
         <v>9.0355529365547006E-3</v>
       </c>
-      <c r="AC5" s="14">
+      <c r="AC5" s="5">
         <v>2.0821056766843499E-2</v>
       </c>
-      <c r="AD5" s="14">
+      <c r="AD5" s="5">
         <v>1.41426045963465E-2</v>
       </c>
-      <c r="AE5" s="14">
+      <c r="AE5" s="5">
         <v>3.2802985660970299E-2</v>
       </c>
-      <c r="AF5" s="14">
-        <v>0</v>
-      </c>
-      <c r="AG5" s="14">
-        <v>0</v>
-      </c>
-      <c r="AH5" s="14">
+      <c r="AF5" s="5">
+        <v>0</v>
+      </c>
+      <c r="AG5" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH5" s="5">
         <v>0.83909032396481398</v>
       </c>
-      <c r="AI5" s="14">
+      <c r="AI5" s="5">
         <v>2.20982621754988E-2</v>
       </c>
-      <c r="AJ5" s="14">
+      <c r="AJ5" s="5">
         <v>4.5054709289851997E-3</v>
       </c>
-      <c r="AK5" s="14">
+      <c r="AK5" s="5">
         <v>5.8356575842094E-2</v>
       </c>
-      <c r="AL5" s="14">
+      <c r="AL5" s="5">
         <v>8.7963956232568093E-3</v>
       </c>
-      <c r="AM5" s="14">
+      <c r="AM5" s="5">
         <v>1.9094614889508699E-2</v>
       </c>
-      <c r="AN5" s="14">
+      <c r="AN5" s="5">
         <v>1.0083673031538299E-2</v>
       </c>
-      <c r="AO5" s="14">
+      <c r="AO5" s="5">
         <v>3.7974683544303799E-2</v>
       </c>
-      <c r="AP5" s="14">
-        <v>0</v>
-      </c>
-      <c r="AQ5" s="14">
-        <v>0</v>
-      </c>
-      <c r="AR5" s="14">
-        <v>0.84293979001499897</v>
-      </c>
-      <c r="AS5" s="14">
-        <v>3.0212127705163901E-2</v>
-      </c>
-      <c r="AT5" s="14">
-        <v>8.3565459610027894E-3</v>
-      </c>
-      <c r="AU5" s="14">
-        <v>4.5211056353117597E-2</v>
-      </c>
-      <c r="AV5" s="14">
-        <v>1.22134133276195E-2</v>
-      </c>
-      <c r="AW5" s="14">
-        <v>2.09985001071352E-2</v>
-      </c>
-      <c r="AX5" s="14">
-        <v>7.9280051424898204E-3</v>
-      </c>
-      <c r="AY5" s="14">
-        <v>3.2140561388472301E-2</v>
-      </c>
-      <c r="AZ5" s="14">
-        <v>0</v>
-      </c>
-      <c r="BA5" s="14">
+      <c r="AP5" s="5">
+        <v>0</v>
+      </c>
+      <c r="AQ5" s="5">
+        <v>0</v>
+      </c>
+      <c r="AR5" s="5">
+        <v>0.84211649242585895</v>
+      </c>
+      <c r="AS5" s="5">
+        <v>2.90164284190314E-2</v>
+      </c>
+      <c r="AT5" s="5">
+        <v>8.7475997439726907E-3</v>
+      </c>
+      <c r="AU5" s="5">
+        <v>4.77917644548752E-2</v>
+      </c>
+      <c r="AV5" s="5">
+        <v>1.19479411137188E-2</v>
+      </c>
+      <c r="AW5" s="5">
+        <v>1.9202048218476601E-2</v>
+      </c>
+      <c r="AX5" s="5">
+        <v>7.6808192873906497E-3</v>
+      </c>
+      <c r="AY5" s="5">
+        <v>3.3496906336675902E-2</v>
+      </c>
+      <c r="AZ5" s="5">
+        <v>0</v>
+      </c>
+      <c r="BA5" s="5">
+        <v>0</v>
+      </c>
+      <c r="BB5" s="5">
+        <v>0.83387688544639205</v>
+      </c>
+      <c r="BC5" s="5">
+        <v>2.85364859355891E-2</v>
+      </c>
+      <c r="BD5" s="5">
+        <v>7.74561761108846E-3</v>
+      </c>
+      <c r="BE5" s="5">
+        <v>6.01304525071341E-2</v>
+      </c>
+      <c r="BF5" s="5">
+        <v>7.1341214838972697E-3</v>
+      </c>
+      <c r="BG5" s="5">
+        <v>1.9364044027721201E-2</v>
+      </c>
+      <c r="BH5" s="5">
+        <v>9.7839380350591108E-3</v>
+      </c>
+      <c r="BI5" s="5">
+        <v>3.3428454953118601E-2</v>
+      </c>
+      <c r="BJ5" s="5">
+        <v>0</v>
+      </c>
+      <c r="BK5" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:53" s="15" customFormat="1">
-      <c r="A6" s="12" t="s">
+    <row r="6" spans="1:63" s="6" customFormat="1">
+      <c r="A6" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B6" s="12" t="s">
+      <c r="B6" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="13" t="s">
+      <c r="C6" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="D6" s="14">
+      <c r="D6" s="5">
         <v>0.71324584785728895</v>
       </c>
-      <c r="E6" s="14">
+      <c r="E6" s="5">
         <v>0.114517121181054</v>
       </c>
-      <c r="F6" s="14">
+      <c r="F6" s="5">
         <v>3.4139840065614102E-2</v>
       </c>
-      <c r="G6" s="14">
+      <c r="G6" s="5">
         <v>7.3918392454377702E-2</v>
       </c>
-      <c r="H6" s="14">
+      <c r="H6" s="5">
         <v>9.0219397170391603E-3</v>
       </c>
-      <c r="I6" s="14">
+      <c r="I6" s="5">
         <v>1.4148041828993201E-2</v>
       </c>
-      <c r="J6" s="14">
+      <c r="J6" s="5">
         <v>7.3815870412138598E-3</v>
       </c>
-      <c r="K6" s="14">
+      <c r="K6" s="5">
         <v>3.3524707812179602E-2</v>
       </c>
-      <c r="L6" s="14">
+      <c r="L6" s="5">
         <v>1.02522042239081E-4</v>
       </c>
-      <c r="M6" s="14">
-        <v>0</v>
-      </c>
-      <c r="N6" s="14">
+      <c r="M6" s="5">
+        <v>0</v>
+      </c>
+      <c r="N6" s="5">
         <v>0.74162995594713699</v>
       </c>
-      <c r="O6" s="14">
+      <c r="O6" s="5">
         <v>0.100550660792952</v>
       </c>
-      <c r="P6" s="14">
+      <c r="P6" s="5">
         <v>2.36784140969163E-2</v>
       </c>
-      <c r="Q6" s="14">
+      <c r="Q6" s="5">
         <v>6.8722466960352405E-2</v>
       </c>
-      <c r="R6" s="14">
+      <c r="R6" s="5">
         <v>9.2511013215858997E-3</v>
       </c>
-      <c r="S6" s="14">
+      <c r="S6" s="5">
         <v>1.35462555066079E-2</v>
       </c>
-      <c r="T6" s="14">
+      <c r="T6" s="5">
         <v>8.2599118942731295E-3</v>
       </c>
-      <c r="U6" s="14">
+      <c r="U6" s="5">
         <v>3.4361233480176202E-2</v>
       </c>
-      <c r="V6" s="14">
-        <v>0</v>
-      </c>
-      <c r="W6" s="14">
-        <v>0</v>
-      </c>
-      <c r="X6" s="14">
+      <c r="V6" s="5">
+        <v>0</v>
+      </c>
+      <c r="W6" s="5">
+        <v>0</v>
+      </c>
+      <c r="X6" s="5">
         <v>0.74017998941238805</v>
       </c>
-      <c r="Y6" s="14">
+      <c r="Y6" s="5">
         <v>0.105346744309158</v>
       </c>
-      <c r="Z6" s="14">
+      <c r="Z6" s="5">
         <v>2.01164637374272E-2</v>
       </c>
-      <c r="AA6" s="14">
+      <c r="AA6" s="5">
         <v>6.78665960825834E-2</v>
       </c>
-      <c r="AB6" s="14">
+      <c r="AB6" s="5">
         <v>7.4113287453679202E-3</v>
       </c>
-      <c r="AC6" s="14">
+      <c r="AC6" s="5">
         <v>1.8528321863419801E-2</v>
       </c>
-      <c r="AD6" s="14">
+      <c r="AD6" s="5">
         <v>1.0375860243515099E-2</v>
       </c>
-      <c r="AE6" s="14">
+      <c r="AE6" s="5">
         <v>3.0174695606140799E-2</v>
       </c>
-      <c r="AF6" s="14">
-        <v>0</v>
-      </c>
-      <c r="AG6" s="14">
-        <v>0</v>
-      </c>
-      <c r="AH6" s="14">
+      <c r="AF6" s="5">
+        <v>0</v>
+      </c>
+      <c r="AG6" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH6" s="5">
         <v>0.74960646447685997</v>
       </c>
-      <c r="AI6" s="14">
+      <c r="AI6" s="5">
         <v>9.2559555042501795E-2</v>
       </c>
-      <c r="AJ6" s="14">
+      <c r="AJ6" s="5">
         <v>1.68957917934726E-2</v>
       </c>
-      <c r="AK6" s="14">
+      <c r="AK6" s="5">
         <v>7.1466051002203795E-2</v>
       </c>
-      <c r="AL6" s="14">
+      <c r="AL6" s="5">
         <v>9.7596809738692402E-3</v>
       </c>
-      <c r="AM6" s="14">
+      <c r="AM6" s="5">
         <v>1.4691992863889201E-2</v>
       </c>
-      <c r="AN6" s="14">
+      <c r="AN6" s="5">
         <v>9.8646237800398794E-3</v>
       </c>
-      <c r="AO6" s="14">
+      <c r="AO6" s="5">
         <v>3.4841011648651499E-2</v>
       </c>
-      <c r="AP6" s="14">
+      <c r="AP6" s="5">
         <v>3.1482841851191101E-4</v>
       </c>
-      <c r="AQ6" s="14">
-        <v>0</v>
-      </c>
-      <c r="AR6" s="14">
-        <v>0.77080123266563905</v>
-      </c>
-      <c r="AS6" s="14">
-        <v>8.1953004622496106E-2</v>
-      </c>
-      <c r="AT6" s="14">
-        <v>1.6082434514637901E-2</v>
-      </c>
-      <c r="AU6" s="14">
-        <v>7.3863636363636395E-2</v>
-      </c>
-      <c r="AV6" s="14">
-        <v>9.3412942989214206E-3</v>
-      </c>
-      <c r="AW6" s="14">
-        <v>1.0593220338983101E-2</v>
-      </c>
-      <c r="AX6" s="14">
-        <v>1.09784283513097E-2</v>
-      </c>
-      <c r="AY6" s="14">
-        <v>2.6386748844376001E-2</v>
-      </c>
-      <c r="AZ6" s="14">
-        <v>0</v>
-      </c>
-      <c r="BA6" s="14">
+      <c r="AQ6" s="5">
+        <v>0</v>
+      </c>
+      <c r="AR6" s="5">
+        <v>0.77362783202199303</v>
+      </c>
+      <c r="AS6" s="5">
+        <v>7.7637690776376903E-2</v>
+      </c>
+      <c r="AT6" s="5">
+        <v>1.6304863020191501E-2</v>
+      </c>
+      <c r="AU6" s="5">
+        <v>7.5457389326002502E-2</v>
+      </c>
+      <c r="AV6" s="5">
+        <v>9.7639586690681599E-3</v>
+      </c>
+      <c r="AW6" s="5">
+        <v>9.5743672386008095E-3</v>
+      </c>
+      <c r="AX6" s="5">
+        <v>9.9535500995354999E-3</v>
+      </c>
+      <c r="AY6" s="5">
+        <v>2.76803488482321E-2</v>
+      </c>
+      <c r="AZ6" s="5">
+        <v>0</v>
+      </c>
+      <c r="BA6" s="5">
+        <v>0</v>
+      </c>
+      <c r="BB6" s="5">
+        <v>0.76361895643848698</v>
+      </c>
+      <c r="BC6" s="5">
+        <v>7.8985160363810397E-2</v>
+      </c>
+      <c r="BD6" s="5">
+        <v>1.8382000957395901E-2</v>
+      </c>
+      <c r="BE6" s="5">
+        <v>7.8027764480612702E-2</v>
+      </c>
+      <c r="BF6" s="5">
+        <v>8.4250837721397808E-3</v>
+      </c>
+      <c r="BG6" s="5">
+        <v>1.11057922450933E-2</v>
+      </c>
+      <c r="BH6" s="5">
+        <v>1.1488750598372399E-2</v>
+      </c>
+      <c r="BI6" s="5">
+        <v>2.99664911440881E-2</v>
+      </c>
+      <c r="BJ6" s="5">
+        <v>0</v>
+      </c>
+      <c r="BK6" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:53" s="15" customFormat="1">
-      <c r="A7" s="12" t="s">
+    <row r="7" spans="1:63" s="6" customFormat="1">
+      <c r="A7" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="12" t="s">
+      <c r="B7" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C7" s="13" t="s">
+      <c r="C7" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="D7" s="14">
+      <c r="D7" s="5">
         <v>0.81634168987929401</v>
       </c>
-      <c r="E7" s="14">
+      <c r="E7" s="5">
         <v>6.3324048282265594E-2</v>
       </c>
-      <c r="F7" s="14">
+      <c r="F7" s="5">
         <v>1.0027855153203299E-2</v>
       </c>
-      <c r="G7" s="14">
+      <c r="G7" s="5">
         <v>2.9340761374187601E-2</v>
       </c>
-      <c r="H7" s="14">
+      <c r="H7" s="5">
         <v>2.63695450324977E-2</v>
       </c>
-      <c r="I7" s="14">
+      <c r="I7" s="5">
         <v>1.15134633240483E-2</v>
       </c>
-      <c r="J7" s="14">
+      <c r="J7" s="5">
         <v>1.41132776230269E-2</v>
       </c>
-      <c r="K7" s="14">
+      <c r="K7" s="5">
         <v>2.72980501392758E-2</v>
       </c>
-      <c r="L7" s="14">
+      <c r="L7" s="5">
         <v>1.6713091922005601E-3</v>
       </c>
-      <c r="M7" s="14">
-        <v>0</v>
-      </c>
-      <c r="N7" s="14">
+      <c r="M7" s="5">
+        <v>0</v>
+      </c>
+      <c r="N7" s="5">
         <v>0.80492546986390101</v>
       </c>
-      <c r="O7" s="14">
+      <c r="O7" s="5">
         <v>7.8850723698422998E-2</v>
       </c>
-      <c r="P7" s="14">
+      <c r="P7" s="5">
         <v>1.23136746597537E-2</v>
       </c>
-      <c r="Q7" s="14">
+      <c r="Q7" s="5">
         <v>2.7651760639447E-2</v>
       </c>
-      <c r="R7" s="14">
+      <c r="R7" s="5">
         <v>1.7498379779649999E-2</v>
       </c>
-      <c r="S7" s="14">
+      <c r="S7" s="5">
         <v>1.42579390797148E-2</v>
       </c>
-      <c r="T7" s="14">
+      <c r="T7" s="5">
         <v>1.83624972996328E-2</v>
       </c>
-      <c r="U7" s="14">
+      <c r="U7" s="5">
         <v>2.54914668394902E-2</v>
       </c>
-      <c r="V7" s="14">
+      <c r="V7" s="5">
         <v>6.4808813998703803E-4</v>
       </c>
-      <c r="W7" s="14">
-        <v>0</v>
-      </c>
-      <c r="X7" s="14">
+      <c r="W7" s="5">
+        <v>0</v>
+      </c>
+      <c r="X7" s="5">
         <v>0.713406873143827</v>
       </c>
-      <c r="Y7" s="14">
+      <c r="Y7" s="5">
         <v>0.15931268561730999</v>
       </c>
-      <c r="Z7" s="14">
+      <c r="Z7" s="5">
         <v>1.6546457361052199E-2</v>
       </c>
-      <c r="AA7" s="14">
+      <c r="AA7" s="5">
         <v>3.03351718285957E-2</v>
       </c>
-      <c r="AB7" s="14">
+      <c r="AB7" s="5">
         <v>1.8667798048366602E-2</v>
       </c>
-      <c r="AC7" s="14">
+      <c r="AC7" s="5">
         <v>1.42129826050064E-2</v>
       </c>
-      <c r="AD7" s="14">
+      <c r="AD7" s="5">
         <v>2.2486211285532499E-2</v>
       </c>
-      <c r="AE7" s="14">
+      <c r="AE7" s="5">
         <v>2.4607551972846801E-2</v>
       </c>
-      <c r="AF7" s="14">
+      <c r="AF7" s="5">
         <v>4.2426813746287702E-4</v>
       </c>
-      <c r="AG7" s="14">
-        <v>0</v>
-      </c>
-      <c r="AH7" s="14">
+      <c r="AG7" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH7" s="5">
         <v>0.69387755102040805</v>
       </c>
-      <c r="AI7" s="14">
+      <c r="AI7" s="5">
         <v>0.14981992797118801</v>
       </c>
-      <c r="AJ7" s="14">
+      <c r="AJ7" s="5">
         <v>2.8571428571428598E-2</v>
       </c>
-      <c r="AK7" s="14">
+      <c r="AK7" s="5">
         <v>2.9291716686674699E-2</v>
       </c>
-      <c r="AL7" s="14">
+      <c r="AL7" s="5">
         <v>1.9927971188475401E-2</v>
       </c>
-      <c r="AM7" s="14">
+      <c r="AM7" s="5">
         <v>1.5366146458583399E-2</v>
       </c>
-      <c r="AN7" s="14">
+      <c r="AN7" s="5">
         <v>2.6410564225690301E-2</v>
       </c>
-      <c r="AO7" s="14">
+      <c r="AO7" s="5">
         <v>3.6734693877551003E-2</v>
       </c>
-      <c r="AP7" s="14">
-        <v>0</v>
-      </c>
-      <c r="AQ7" s="14">
-        <v>0</v>
-      </c>
-      <c r="AR7" s="14">
-        <v>0.69556886227544901</v>
-      </c>
-      <c r="AS7" s="14">
-        <v>0.154251497005988</v>
-      </c>
-      <c r="AT7" s="14">
-        <v>2.9940119760479E-2</v>
-      </c>
-      <c r="AU7" s="14">
-        <v>3.2335329341317401E-2</v>
-      </c>
-      <c r="AV7" s="14">
-        <v>1.29341317365269E-2</v>
-      </c>
-      <c r="AW7" s="14">
-        <v>1.55688622754491E-2</v>
-      </c>
-      <c r="AX7" s="14">
-        <v>2.61077844311377E-2</v>
-      </c>
-      <c r="AY7" s="14">
-        <v>3.3293413173652697E-2</v>
-      </c>
-      <c r="AZ7" s="14">
-        <v>0</v>
-      </c>
-      <c r="BA7" s="14">
-        <v>0</v>
+      <c r="AP7" s="5">
+        <v>0</v>
+      </c>
+      <c r="AQ7" s="5">
+        <v>0</v>
+      </c>
+      <c r="AR7" s="5">
+        <v>0.68772782503037699</v>
+      </c>
+      <c r="AS7" s="5">
+        <v>0.15698663426488499</v>
+      </c>
+      <c r="AT7" s="5">
+        <v>3.1348724179829902E-2</v>
+      </c>
+      <c r="AU7" s="5">
+        <v>3.5722964763061998E-2</v>
+      </c>
+      <c r="AV7" s="5">
+        <v>1.16646415552855E-2</v>
+      </c>
+      <c r="AW7" s="5">
+        <v>1.62818955042527E-2</v>
+      </c>
+      <c r="AX7" s="5">
+        <v>2.8189550425273401E-2</v>
+      </c>
+      <c r="AY7" s="5">
+        <v>3.2077764277035202E-2</v>
+      </c>
+      <c r="AZ7" s="5">
+        <v>0</v>
+      </c>
+      <c r="BA7" s="5">
+        <v>0</v>
+      </c>
+      <c r="BB7" s="5">
+        <v>0.71409714889123499</v>
+      </c>
+      <c r="BC7" s="5">
+        <v>0.14994720168954601</v>
+      </c>
+      <c r="BD7" s="5">
+        <v>2.69271383315734E-2</v>
+      </c>
+      <c r="BE7" s="5">
+        <v>3.2734952481520599E-2</v>
+      </c>
+      <c r="BF7" s="5">
+        <v>1.16156282998944E-2</v>
+      </c>
+      <c r="BG7" s="5">
+        <v>1.1879619852164699E-2</v>
+      </c>
+      <c r="BH7" s="5">
+        <v>1.92713833157339E-2</v>
+      </c>
+      <c r="BI7" s="5">
+        <v>3.2470960929250302E-2</v>
+      </c>
+      <c r="BJ7" s="5">
+        <v>0</v>
+      </c>
+      <c r="BK7" s="5">
+        <v>1.05596620908131E-3</v>
       </c>
     </row>
-    <row r="8" spans="1:53" s="15" customFormat="1">
-      <c r="A8" s="12" t="s">
+    <row r="8" spans="1:63" s="6" customFormat="1">
+      <c r="A8" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B8" s="12" t="s">
+      <c r="B8" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C8" s="13" t="s">
+      <c r="C8" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="D8" s="14">
+      <c r="D8" s="5">
         <v>0.32124999999999998</v>
       </c>
-      <c r="E8" s="14">
+      <c r="E8" s="5">
         <v>0.47375</v>
       </c>
-      <c r="F8" s="14">
+      <c r="F8" s="5">
         <v>1.25E-3</v>
       </c>
-      <c r="G8" s="14">
+      <c r="G8" s="5">
         <v>0.16625000000000001</v>
       </c>
-      <c r="H8" s="14">
+      <c r="H8" s="5">
         <v>2.375E-2</v>
       </c>
-      <c r="I8" s="14">
-        <v>0</v>
-      </c>
-      <c r="J8" s="14">
-        <v>0</v>
-      </c>
-      <c r="K8" s="14">
+      <c r="I8" s="5">
+        <v>0</v>
+      </c>
+      <c r="J8" s="5">
+        <v>0</v>
+      </c>
+      <c r="K8" s="5">
         <v>1.375E-2</v>
       </c>
-      <c r="L8" s="14">
-        <v>0</v>
-      </c>
-      <c r="M8" s="14">
-        <v>0</v>
-      </c>
-      <c r="N8" s="14">
+      <c r="L8" s="5">
+        <v>0</v>
+      </c>
+      <c r="M8" s="5">
+        <v>0</v>
+      </c>
+      <c r="N8" s="5">
         <v>0.29878869448182999</v>
       </c>
-      <c r="O8" s="14">
+      <c r="O8" s="5">
         <v>0.51951547779273199</v>
       </c>
-      <c r="P8" s="14">
+      <c r="P8" s="5">
         <v>5.3835800807537004E-3</v>
       </c>
-      <c r="Q8" s="14">
+      <c r="Q8" s="5">
         <v>0.15612382234185701</v>
       </c>
-      <c r="R8" s="14">
+      <c r="R8" s="5">
         <v>1.34589502018843E-2</v>
       </c>
-      <c r="S8" s="14">
+      <c r="S8" s="5">
         <v>2.6917900403768502E-3</v>
       </c>
-      <c r="T8" s="14">
-        <v>0</v>
-      </c>
-      <c r="U8" s="14">
+      <c r="T8" s="5">
+        <v>0</v>
+      </c>
+      <c r="U8" s="5">
         <v>4.0376850605652803E-3</v>
       </c>
-      <c r="V8" s="14">
-        <v>0</v>
-      </c>
-      <c r="W8" s="14">
-        <v>0</v>
-      </c>
-      <c r="X8" s="14">
+      <c r="V8" s="5">
+        <v>0</v>
+      </c>
+      <c r="W8" s="5">
+        <v>0</v>
+      </c>
+      <c r="X8" s="5">
         <v>0.32451093210586901</v>
       </c>
-      <c r="Y8" s="14">
+      <c r="Y8" s="5">
         <v>0.495972382048331</v>
       </c>
-      <c r="Z8" s="14">
-        <v>0</v>
-      </c>
-      <c r="AA8" s="14">
+      <c r="Z8" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA8" s="5">
         <v>0.15535097813578799</v>
       </c>
-      <c r="AB8" s="14">
+      <c r="AB8" s="5">
         <v>1.03567318757192E-2</v>
       </c>
-      <c r="AC8" s="14">
+      <c r="AC8" s="5">
         <v>3.4522439585730701E-3</v>
       </c>
-      <c r="AD8" s="14">
-        <v>0</v>
-      </c>
-      <c r="AE8" s="14">
+      <c r="AD8" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE8" s="5">
         <v>1.03567318757192E-2</v>
       </c>
-      <c r="AF8" s="14">
-        <v>0</v>
-      </c>
-      <c r="AG8" s="14">
-        <v>0</v>
-      </c>
-      <c r="AH8" s="14">
+      <c r="AF8" s="5">
+        <v>0</v>
+      </c>
+      <c r="AG8" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH8" s="5">
         <v>0.35872235872235902</v>
       </c>
-      <c r="AI8" s="14">
+      <c r="AI8" s="5">
         <v>0.46314496314496301</v>
       </c>
-      <c r="AJ8" s="14">
-        <v>0</v>
-      </c>
-      <c r="AK8" s="14">
+      <c r="AJ8" s="5">
+        <v>0</v>
+      </c>
+      <c r="AK8" s="5">
         <v>0.15479115479115499</v>
       </c>
-      <c r="AL8" s="14">
+      <c r="AL8" s="5">
         <v>1.7199017199017199E-2</v>
       </c>
-      <c r="AM8" s="14">
-        <v>0</v>
-      </c>
-      <c r="AN8" s="14">
-        <v>0</v>
-      </c>
-      <c r="AO8" s="14">
+      <c r="AM8" s="5">
+        <v>0</v>
+      </c>
+      <c r="AN8" s="5">
+        <v>0</v>
+      </c>
+      <c r="AO8" s="5">
         <v>6.1425061425061404E-3</v>
       </c>
-      <c r="AP8" s="14">
-        <v>0</v>
-      </c>
-      <c r="AQ8" s="14">
-        <v>0</v>
-      </c>
-      <c r="AR8" s="14">
-        <v>0.37825594563986398</v>
-      </c>
-      <c r="AS8" s="14">
-        <v>0.45300113250283103</v>
-      </c>
-      <c r="AT8" s="14">
-        <v>0</v>
-      </c>
-      <c r="AU8" s="14">
-        <v>0.143827859569649</v>
-      </c>
-      <c r="AV8" s="14">
-        <v>1.13250283125708E-2</v>
-      </c>
-      <c r="AW8" s="14">
-        <v>2.2650056625141599E-3</v>
-      </c>
-      <c r="AX8" s="14">
-        <v>0</v>
-      </c>
-      <c r="AY8" s="14">
-        <v>1.13250283125708E-2</v>
-      </c>
-      <c r="AZ8" s="14">
-        <v>0</v>
-      </c>
-      <c r="BA8" s="14">
+      <c r="AP8" s="5">
+        <v>0</v>
+      </c>
+      <c r="AQ8" s="5">
+        <v>0</v>
+      </c>
+      <c r="AR8" s="5">
+        <v>0.36383682469680301</v>
+      </c>
+      <c r="AS8" s="5">
+        <v>0.46857772877618498</v>
+      </c>
+      <c r="AT8" s="5">
+        <v>0</v>
+      </c>
+      <c r="AU8" s="5">
+        <v>0.14332965821389199</v>
+      </c>
+      <c r="AV8" s="5">
+        <v>1.32304299889746E-2</v>
+      </c>
+      <c r="AW8" s="5">
+        <v>2.20507166482911E-3</v>
+      </c>
+      <c r="AX8" s="5">
+        <v>0</v>
+      </c>
+      <c r="AY8" s="5">
+        <v>8.8202866593164297E-3</v>
+      </c>
+      <c r="AZ8" s="5">
+        <v>0</v>
+      </c>
+      <c r="BA8" s="5">
+        <v>0</v>
+      </c>
+      <c r="BB8" s="5">
+        <v>0.56646394439617698</v>
+      </c>
+      <c r="BC8" s="5">
+        <v>0.30147697654213701</v>
+      </c>
+      <c r="BD8" s="5">
+        <v>0</v>
+      </c>
+      <c r="BE8" s="5">
+        <v>0.106863596872285</v>
+      </c>
+      <c r="BF8" s="5">
+        <v>1.12945264986968E-2</v>
+      </c>
+      <c r="BG8" s="5">
+        <v>2.6064291920069498E-3</v>
+      </c>
+      <c r="BH8" s="5">
+        <v>8.6880973066898301E-4</v>
+      </c>
+      <c r="BI8" s="5">
+        <v>8.6880973066898407E-3</v>
+      </c>
+      <c r="BJ8" s="5">
+        <v>1.7376194613379699E-3</v>
+      </c>
+      <c r="BK8" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:53" s="15" customFormat="1">
-      <c r="A9" s="12" t="s">
+    <row r="9" spans="1:63" s="6" customFormat="1">
+      <c r="A9" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B9" s="12" t="s">
+      <c r="B9" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C9" s="13" t="s">
+      <c r="C9" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D9" s="14">
+      <c r="D9" s="5">
         <v>0.67042571186918498</v>
       </c>
-      <c r="E9" s="14">
+      <c r="E9" s="5">
         <v>9.0499013250634294E-2</v>
       </c>
-      <c r="F9" s="14">
+      <c r="F9" s="5">
         <v>9.3036368762334398E-2</v>
       </c>
-      <c r="G9" s="14">
+      <c r="G9" s="5">
         <v>3.21398364815337E-2</v>
       </c>
-      <c r="H9" s="14">
+      <c r="H9" s="5">
         <v>2.31181279954891E-2</v>
       </c>
-      <c r="I9" s="14">
+      <c r="I9" s="5">
         <v>1.8325345362277999E-2</v>
       </c>
-      <c r="J9" s="14">
+      <c r="J9" s="5">
         <v>1.7479560191711301E-2</v>
       </c>
-      <c r="K9" s="14">
+      <c r="K9" s="5">
         <v>5.4694107696645101E-2</v>
       </c>
-      <c r="L9" s="14">
+      <c r="L9" s="5">
         <v>2.8192839018889202E-4</v>
       </c>
-      <c r="M9" s="14">
-        <v>0</v>
-      </c>
-      <c r="N9" s="14">
+      <c r="M9" s="5">
+        <v>0</v>
+      </c>
+      <c r="N9" s="5">
         <v>0.719868735083532</v>
       </c>
-      <c r="O9" s="14">
+      <c r="O9" s="5">
         <v>8.8007159904534601E-2</v>
       </c>
-      <c r="P9" s="14">
+      <c r="P9" s="5">
         <v>6.6825775656324596E-2</v>
       </c>
-      <c r="Q9" s="14">
+      <c r="Q9" s="5">
         <v>3.0727923627684998E-2</v>
       </c>
-      <c r="R9" s="14">
+      <c r="R9" s="5">
         <v>1.49164677804296E-2</v>
       </c>
-      <c r="S9" s="14">
+      <c r="S9" s="5">
         <v>1.49164677804296E-2</v>
       </c>
-      <c r="T9" s="14">
+      <c r="T9" s="5">
         <v>1.8496420047732699E-2</v>
       </c>
-      <c r="U9" s="14">
+      <c r="U9" s="5">
         <v>4.6241050119331703E-2</v>
       </c>
-      <c r="V9" s="14">
-        <v>0</v>
-      </c>
-      <c r="W9" s="14">
-        <v>0</v>
-      </c>
-      <c r="X9" s="14">
+      <c r="V9" s="5">
+        <v>0</v>
+      </c>
+      <c r="W9" s="5">
+        <v>0</v>
+      </c>
+      <c r="X9" s="5">
         <v>0.74807277212457601</v>
       </c>
-      <c r="Y9" s="14">
+      <c r="Y9" s="5">
         <v>9.0348442799876694E-2</v>
       </c>
-      <c r="Z9" s="14">
+      <c r="Z9" s="5">
         <v>4.16281221091582E-2</v>
       </c>
-      <c r="AA9" s="14">
+      <c r="AA9" s="5">
         <v>2.8985507246376802E-2</v>
       </c>
-      <c r="AB9" s="14">
+      <c r="AB9" s="5">
         <v>1.63428923835954E-2</v>
       </c>
-      <c r="AC9" s="14">
+      <c r="AC9" s="5">
         <v>1.20259019426457E-2</v>
       </c>
-      <c r="AD9" s="14">
+      <c r="AD9" s="5">
         <v>1.3259327782917101E-2</v>
       </c>
-      <c r="AE9" s="14">
+      <c r="AE9" s="5">
         <v>4.9337033610854099E-2</v>
       </c>
-      <c r="AF9" s="14">
-        <v>0</v>
-      </c>
-      <c r="AG9" s="14">
-        <v>0</v>
-      </c>
-      <c r="AH9" s="14">
+      <c r="AF9" s="5">
+        <v>0</v>
+      </c>
+      <c r="AG9" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH9" s="5">
         <v>0.704199066874028</v>
       </c>
-      <c r="AI9" s="14">
+      <c r="AI9" s="5">
         <v>0.101710730948678</v>
       </c>
-      <c r="AJ9" s="14">
+      <c r="AJ9" s="5">
         <v>5.7542768273717002E-2</v>
       </c>
-      <c r="AK9" s="14">
+      <c r="AK9" s="5">
         <v>3.7636080870917597E-2</v>
       </c>
-      <c r="AL9" s="14">
+      <c r="AL9" s="5">
         <v>1.8662519440124401E-2</v>
       </c>
-      <c r="AM9" s="14">
+      <c r="AM9" s="5">
         <v>1.43079315707621E-2</v>
       </c>
-      <c r="AN9" s="14">
+      <c r="AN9" s="5">
         <v>1.89735614307932E-2</v>
       </c>
-      <c r="AO9" s="14">
+      <c r="AO9" s="5">
         <v>4.6967340590979803E-2</v>
       </c>
-      <c r="AP9" s="14">
-        <v>0</v>
-      </c>
-      <c r="AQ9" s="14">
-        <v>0</v>
-      </c>
-      <c r="AR9" s="14">
-        <v>0.70510795155344896</v>
-      </c>
-      <c r="AS9" s="14">
-        <v>0.114533965244866</v>
-      </c>
-      <c r="AT9" s="14">
-        <v>5.0816219062664598E-2</v>
-      </c>
-      <c r="AU9" s="14">
-        <v>3.7124802527646099E-2</v>
-      </c>
-      <c r="AV9" s="14">
-        <v>2.0273828330700398E-2</v>
-      </c>
-      <c r="AW9" s="14">
-        <v>1.5534491837809399E-2</v>
-      </c>
-      <c r="AX9" s="14">
-        <v>1.7640863612427601E-2</v>
-      </c>
-      <c r="AY9" s="14">
-        <v>3.8704581358609803E-2</v>
-      </c>
-      <c r="AZ9" s="14">
-        <v>2.63296471827277E-4</v>
-      </c>
-      <c r="BA9" s="14">
-        <v>0</v>
+      <c r="AP9" s="5">
+        <v>0</v>
+      </c>
+      <c r="AQ9" s="5">
+        <v>0</v>
+      </c>
+      <c r="AR9" s="5">
+        <v>0.70299796747967502</v>
+      </c>
+      <c r="AS9" s="5">
+        <v>0.114329268292683</v>
+      </c>
+      <c r="AT9" s="5">
+        <v>5.1321138211382102E-2</v>
+      </c>
+      <c r="AU9" s="5">
+        <v>3.9888211382113799E-2</v>
+      </c>
+      <c r="AV9" s="5">
+        <v>1.9817073170731701E-2</v>
+      </c>
+      <c r="AW9" s="5">
+        <v>1.54979674796748E-2</v>
+      </c>
+      <c r="AX9" s="5">
+        <v>1.88008130081301E-2</v>
+      </c>
+      <c r="AY9" s="5">
+        <v>3.7093495934959399E-2</v>
+      </c>
+      <c r="AZ9" s="5">
+        <v>2.5406504065040702E-4</v>
+      </c>
+      <c r="BA9" s="5">
+        <v>0</v>
+      </c>
+      <c r="BB9" s="5">
+        <v>0.65848112778535695</v>
+      </c>
+      <c r="BC9" s="5">
+        <v>0.13324238290131901</v>
+      </c>
+      <c r="BD9" s="5">
+        <v>6.3210550250113698E-2</v>
+      </c>
+      <c r="BE9" s="5">
+        <v>4.5020463847203297E-2</v>
+      </c>
+      <c r="BF9" s="5">
+        <v>2.4329240563892698E-2</v>
+      </c>
+      <c r="BG9" s="5">
+        <v>1.5461573442473901E-2</v>
+      </c>
+      <c r="BH9" s="5">
+        <v>2.3647112323783501E-2</v>
+      </c>
+      <c r="BI9" s="5">
+        <v>3.4333788085493401E-2</v>
+      </c>
+      <c r="BJ9" s="5">
+        <v>9.0950432014552099E-4</v>
+      </c>
+      <c r="BK9" s="5">
+        <v>1.36425648021828E-3</v>
       </c>
     </row>
-    <row r="10" spans="1:53" s="15" customFormat="1">
-      <c r="A10" s="12" t="s">
+    <row r="10" spans="1:63" s="6" customFormat="1">
+      <c r="A10" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B10" s="12" t="s">
+      <c r="B10" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C10" s="13" t="s">
+      <c r="C10" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="D10" s="14">
+      <c r="D10" s="5">
         <v>0.78190543903306098</v>
       </c>
-      <c r="E10" s="14">
+      <c r="E10" s="5">
         <v>5.7412015641663698E-2</v>
       </c>
-      <c r="F10" s="14">
+      <c r="F10" s="5">
         <v>6.9854248133665101E-2</v>
       </c>
-      <c r="G10" s="14">
+      <c r="G10" s="5">
         <v>3.1461073586917902E-2</v>
       </c>
-      <c r="H10" s="14">
+      <c r="H10" s="5">
         <v>5.5101315321720596E-3</v>
       </c>
-      <c r="I10" s="14">
+      <c r="I10" s="5">
         <v>2.3107003199431199E-3</v>
       </c>
-      <c r="J10" s="14">
+      <c r="J10" s="5">
         <v>1.35087095627444E-2</v>
       </c>
-      <c r="K10" s="14">
+      <c r="K10" s="5">
         <v>3.7148951297547098E-2</v>
       </c>
-      <c r="L10" s="14">
+      <c r="L10" s="5">
         <v>5.3323853537148999E-4</v>
       </c>
-      <c r="M10" s="14">
+      <c r="M10" s="5">
         <v>3.5549235691432601E-4</v>
       </c>
-      <c r="N10" s="14">
+      <c r="N10" s="5">
         <v>0.79769262463947299</v>
       </c>
-      <c r="O10" s="14">
+      <c r="O10" s="5">
         <v>4.8413679439637397E-2</v>
       </c>
-      <c r="P10" s="14">
+      <c r="P10" s="5">
         <v>4.8619695096827398E-2</v>
       </c>
-      <c r="Q10" s="14">
+      <c r="Q10" s="5">
         <v>3.0902348578492E-2</v>
       </c>
-      <c r="R10" s="14">
+      <c r="R10" s="5">
         <v>1.1124845488257099E-2</v>
       </c>
-      <c r="S10" s="14">
+      <c r="S10" s="5">
         <v>3.5022661722290899E-3</v>
       </c>
-      <c r="T10" s="14">
+      <c r="T10" s="5">
         <v>1.48331273176761E-2</v>
       </c>
-      <c r="U10" s="14">
+      <c r="U10" s="5">
         <v>4.3469303667078699E-2</v>
       </c>
-      <c r="V10" s="14">
+      <c r="V10" s="5">
         <v>6.1804697156983904E-4</v>
       </c>
-      <c r="W10" s="14">
+      <c r="W10" s="5">
         <v>8.2406262875978596E-4</v>
       </c>
-      <c r="X10" s="14">
+      <c r="X10" s="5">
         <v>0.79055150040551503</v>
       </c>
-      <c r="Y10" s="14">
+      <c r="Y10" s="5">
         <v>0.104420113544201</v>
       </c>
-      <c r="Z10" s="14">
+      <c r="Z10" s="5">
         <v>1.0137875101378801E-2</v>
       </c>
-      <c r="AA10" s="14">
+      <c r="AA10" s="5">
         <v>2.6155717761557201E-2</v>
       </c>
-      <c r="AB10" s="14">
+      <c r="AB10" s="5">
         <v>6.0827250608272501E-3</v>
       </c>
-      <c r="AC10" s="14">
+      <c r="AC10" s="5">
         <v>1.4193025141930301E-3</v>
       </c>
-      <c r="AD10" s="14">
+      <c r="AD10" s="5">
         <v>1.4801297648013001E-2</v>
       </c>
-      <c r="AE10" s="14">
+      <c r="AE10" s="5">
         <v>4.56204379562044E-2</v>
       </c>
-      <c r="AF10" s="14">
+      <c r="AF10" s="5">
         <v>8.1103000811029999E-4</v>
       </c>
-      <c r="AG10" s="14">
-        <v>0</v>
-      </c>
-      <c r="AH10" s="14">
+      <c r="AG10" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH10" s="5">
         <v>0.82323125659978902</v>
       </c>
-      <c r="AI10" s="14">
+      <c r="AI10" s="5">
         <v>8.02534318901795E-2</v>
       </c>
-      <c r="AJ10" s="14">
+      <c r="AJ10" s="5">
         <v>2.5343189017951401E-3</v>
       </c>
-      <c r="AK10" s="14">
+      <c r="AK10" s="5">
         <v>2.82998944033791E-2</v>
       </c>
-      <c r="AL10" s="14">
+      <c r="AL10" s="5">
         <v>7.1805702217528997E-3</v>
       </c>
-      <c r="AM10" s="14">
+      <c r="AM10" s="5">
         <v>3.5902851108764499E-3</v>
       </c>
-      <c r="AN10" s="14">
+      <c r="AN10" s="5">
         <v>1.09820485744456E-2</v>
       </c>
-      <c r="AO10" s="14">
+      <c r="AO10" s="5">
         <v>4.3294614572333703E-2</v>
       </c>
-      <c r="AP10" s="14">
-        <v>0</v>
-      </c>
-      <c r="AQ10" s="14">
+      <c r="AP10" s="5">
+        <v>0</v>
+      </c>
+      <c r="AQ10" s="5">
         <v>6.33579725448786E-4</v>
       </c>
-      <c r="AR10" s="14">
-        <v>0.83475232198142402</v>
-      </c>
-      <c r="AS10" s="14">
-        <v>7.4303405572755402E-2</v>
-      </c>
-      <c r="AT10" s="14">
-        <v>5.6114551083591303E-3</v>
-      </c>
-      <c r="AU10" s="14">
-        <v>2.6122291021671799E-2</v>
-      </c>
-      <c r="AV10" s="14">
-        <v>5.4179566563467502E-3</v>
-      </c>
-      <c r="AW10" s="14">
-        <v>4.2569659442724499E-3</v>
-      </c>
-      <c r="AX10" s="14">
-        <v>9.2879256965944304E-3</v>
-      </c>
-      <c r="AY10" s="14">
-        <v>3.98606811145511E-2</v>
-      </c>
-      <c r="AZ10" s="14">
-        <v>1.9349845201238399E-4</v>
-      </c>
-      <c r="BA10" s="14">
-        <v>1.9349845201238399E-4</v>
+      <c r="AR10" s="5">
+        <v>0.81956315289648596</v>
+      </c>
+      <c r="AS10" s="5">
+        <v>8.6989553656220298E-2</v>
+      </c>
+      <c r="AT10" s="5">
+        <v>5.8879392212725602E-3</v>
+      </c>
+      <c r="AU10" s="5">
+        <v>2.5451092117758801E-2</v>
+      </c>
+      <c r="AV10" s="5">
+        <v>6.64767331433998E-3</v>
+      </c>
+      <c r="AW10" s="5">
+        <v>5.5080721747388399E-3</v>
+      </c>
+      <c r="AX10" s="5">
+        <v>9.1168091168091197E-3</v>
+      </c>
+      <c r="AY10" s="5">
+        <v>4.0455840455840497E-2</v>
+      </c>
+      <c r="AZ10" s="5">
+        <v>1.8993352326685699E-4</v>
+      </c>
+      <c r="BA10" s="5">
+        <v>1.8993352326685699E-4</v>
+      </c>
+      <c r="BB10" s="5">
+        <v>0.62018804328543597</v>
+      </c>
+      <c r="BC10" s="5">
+        <v>0.28046833422033002</v>
+      </c>
+      <c r="BD10" s="5">
+        <v>9.4021642717757696E-3</v>
+      </c>
+      <c r="BE10" s="5">
+        <v>2.4658506297676099E-2</v>
+      </c>
+      <c r="BF10" s="5">
+        <v>6.5637750576547802E-3</v>
+      </c>
+      <c r="BG10" s="5">
+        <v>1.25953521376619E-2</v>
+      </c>
+      <c r="BH10" s="5">
+        <v>7.6281710129501501E-3</v>
+      </c>
+      <c r="BI10" s="5">
+        <v>3.83182543906333E-2</v>
+      </c>
+      <c r="BJ10" s="5">
+        <v>0</v>
+      </c>
+      <c r="BK10" s="5">
+        <v>1.77399325882562E-4</v>
       </c>
     </row>
-    <row r="11" spans="1:53" s="15" customFormat="1">
-      <c r="A11" s="12" t="s">
+    <row r="11" spans="1:63" s="6" customFormat="1">
+      <c r="A11" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B11" s="12" t="s">
+      <c r="B11" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C11" s="13" t="s">
+      <c r="C11" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="D11" s="14">
+      <c r="D11" s="5">
         <v>0.54591194968553503</v>
       </c>
-      <c r="E11" s="14">
+      <c r="E11" s="5">
         <v>0.13710691823899401</v>
       </c>
-      <c r="F11" s="14">
+      <c r="F11" s="5">
         <v>0.167295597484277</v>
       </c>
-      <c r="G11" s="14">
+      <c r="G11" s="5">
         <v>6.7924528301886805E-2</v>
       </c>
-      <c r="H11" s="14">
+      <c r="H11" s="5">
         <v>7.5471698113207496E-3</v>
       </c>
-      <c r="I11" s="14">
+      <c r="I11" s="5">
         <v>5.0314465408805003E-3</v>
       </c>
-      <c r="J11" s="14">
-        <v>0</v>
-      </c>
-      <c r="K11" s="14">
+      <c r="J11" s="5">
+        <v>0</v>
+      </c>
+      <c r="K11" s="5">
         <v>6.9182389937106903E-2</v>
       </c>
-      <c r="L11" s="14">
-        <v>0</v>
-      </c>
-      <c r="M11" s="14">
-        <v>0</v>
-      </c>
-      <c r="N11" s="14">
+      <c r="L11" s="5">
+        <v>0</v>
+      </c>
+      <c r="M11" s="5">
+        <v>0</v>
+      </c>
+      <c r="N11" s="5">
         <v>0.55591054313098998</v>
       </c>
-      <c r="O11" s="14">
+      <c r="O11" s="5">
         <v>0.12619808306709299</v>
       </c>
-      <c r="P11" s="14">
+      <c r="P11" s="5">
         <v>0.12779552715654999</v>
       </c>
-      <c r="Q11" s="14">
+      <c r="Q11" s="5">
         <v>0.10702875399361</v>
       </c>
-      <c r="R11" s="14">
+      <c r="R11" s="5">
         <v>4.7923322683706103E-3</v>
       </c>
-      <c r="S11" s="14">
+      <c r="S11" s="5">
         <v>1.75718849840256E-2</v>
       </c>
-      <c r="T11" s="14">
+      <c r="T11" s="5">
         <v>1.59744408945687E-3</v>
       </c>
-      <c r="U11" s="14">
+      <c r="U11" s="5">
         <v>5.9105431309904199E-2</v>
       </c>
-      <c r="V11" s="14">
-        <v>0</v>
-      </c>
-      <c r="W11" s="14">
-        <v>0</v>
-      </c>
-      <c r="X11" s="14">
+      <c r="V11" s="5">
+        <v>0</v>
+      </c>
+      <c r="W11" s="5">
+        <v>0</v>
+      </c>
+      <c r="X11" s="5">
         <v>0.61833105335157301</v>
       </c>
-      <c r="Y11" s="14">
+      <c r="Y11" s="5">
         <v>9.7127222982216099E-2</v>
       </c>
-      <c r="Z11" s="14">
+      <c r="Z11" s="5">
         <v>0.14363885088919301</v>
       </c>
-      <c r="AA11" s="14">
+      <c r="AA11" s="5">
         <v>5.19835841313269E-2</v>
       </c>
-      <c r="AB11" s="14">
+      <c r="AB11" s="5">
         <v>9.5759233926128607E-3</v>
       </c>
-      <c r="AC11" s="14">
+      <c r="AC11" s="5">
         <v>1.3679890560875501E-2</v>
       </c>
-      <c r="AD11" s="14">
+      <c r="AD11" s="5">
         <v>1.36798905608755E-3</v>
       </c>
-      <c r="AE11" s="14">
+      <c r="AE11" s="5">
         <v>6.4295485636114896E-2</v>
       </c>
-      <c r="AF11" s="14">
-        <v>0</v>
-      </c>
-      <c r="AG11" s="14">
-        <v>0</v>
-      </c>
-      <c r="AH11" s="14">
+      <c r="AF11" s="5">
+        <v>0</v>
+      </c>
+      <c r="AG11" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH11" s="5">
         <v>0.69309462915600994</v>
       </c>
-      <c r="AI11" s="14">
+      <c r="AI11" s="5">
         <v>0.138107416879795</v>
       </c>
-      <c r="AJ11" s="14">
+      <c r="AJ11" s="5">
         <v>6.7774936061381102E-2</v>
       </c>
-      <c r="AK11" s="14">
+      <c r="AK11" s="5">
         <v>3.5805626598465499E-2</v>
       </c>
-      <c r="AL11" s="14">
+      <c r="AL11" s="5">
         <v>5.1150895140665001E-3</v>
       </c>
-      <c r="AM11" s="14">
+      <c r="AM11" s="5">
         <v>1.5345268542199499E-2</v>
       </c>
-      <c r="AN11" s="14">
-        <v>0</v>
-      </c>
-      <c r="AO11" s="14">
+      <c r="AN11" s="5">
+        <v>0</v>
+      </c>
+      <c r="AO11" s="5">
         <v>4.3478260869565202E-2</v>
       </c>
-      <c r="AP11" s="14">
-        <v>0</v>
-      </c>
-      <c r="AQ11" s="14">
+      <c r="AP11" s="5">
+        <v>0</v>
+      </c>
+      <c r="AQ11" s="5">
         <v>1.27877237851662E-3</v>
       </c>
-      <c r="AR11" s="14">
-        <v>0.61567635903919105</v>
-      </c>
-      <c r="AS11" s="14">
-        <v>0.13527180783817999</v>
-      </c>
-      <c r="AT11" s="14">
-        <v>0.106194690265487</v>
-      </c>
-      <c r="AU11" s="14">
-        <v>5.3097345132743397E-2</v>
-      </c>
-      <c r="AV11" s="14">
-        <v>2.5284450063211101E-3</v>
-      </c>
-      <c r="AW11" s="14">
-        <v>1.5170670037926701E-2</v>
-      </c>
-      <c r="AX11" s="14">
-        <v>1.39064475347661E-2</v>
-      </c>
-      <c r="AY11" s="14">
-        <v>5.8154235145385598E-2</v>
-      </c>
-      <c r="AZ11" s="14">
-        <v>0</v>
-      </c>
-      <c r="BA11" s="14">
+      <c r="AR11" s="5">
+        <v>0.59006211180124202</v>
+      </c>
+      <c r="AS11" s="5">
+        <v>0.140372670807453</v>
+      </c>
+      <c r="AT11" s="5">
+        <v>0.121739130434783</v>
+      </c>
+      <c r="AU11" s="5">
+        <v>5.5900621118012403E-2</v>
+      </c>
+      <c r="AV11" s="5">
+        <v>1.2422360248447199E-3</v>
+      </c>
+      <c r="AW11" s="5">
+        <v>1.4906832298136601E-2</v>
+      </c>
+      <c r="AX11" s="5">
+        <v>1.6149068322981401E-2</v>
+      </c>
+      <c r="AY11" s="5">
+        <v>5.9627329192546603E-2</v>
+      </c>
+      <c r="AZ11" s="5">
+        <v>0</v>
+      </c>
+      <c r="BA11" s="5">
+        <v>0</v>
+      </c>
+      <c r="BB11" s="5">
+        <v>0.62022471910112398</v>
+      </c>
+      <c r="BC11" s="5">
+        <v>0.14606741573033699</v>
+      </c>
+      <c r="BD11" s="5">
+        <v>9.6629213483146098E-2</v>
+      </c>
+      <c r="BE11" s="5">
+        <v>4.2696629213483099E-2</v>
+      </c>
+      <c r="BF11" s="5">
+        <v>4.4943820224719096E-3</v>
+      </c>
+      <c r="BG11" s="5">
+        <v>1.23595505617978E-2</v>
+      </c>
+      <c r="BH11" s="5">
+        <v>1.1235955056179799E-2</v>
+      </c>
+      <c r="BI11" s="5">
+        <v>6.6292134831460695E-2</v>
+      </c>
+      <c r="BJ11" s="5">
+        <v>0</v>
+      </c>
+      <c r="BK11" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:53" s="15" customFormat="1">
-      <c r="A12" s="12" t="s">
+    <row r="12" spans="1:63" s="6" customFormat="1">
+      <c r="A12" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B12" s="12" t="s">
+      <c r="B12" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C12" s="13" t="s">
+      <c r="C12" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="D12" s="14">
+      <c r="D12" s="5">
         <v>0.79780219780219797</v>
       </c>
-      <c r="E12" s="14">
+      <c r="E12" s="5">
         <v>4.1758241758241797E-2</v>
       </c>
-      <c r="F12" s="14">
+      <c r="F12" s="5">
         <v>6.3736263736263704E-2</v>
       </c>
-      <c r="G12" s="14">
+      <c r="G12" s="5">
         <v>3.2967032967033003E-2</v>
       </c>
-      <c r="H12" s="14">
+      <c r="H12" s="5">
         <v>6.5934065934065899E-3</v>
       </c>
-      <c r="I12" s="14">
+      <c r="I12" s="5">
         <v>1.5384615384615399E-2</v>
       </c>
-      <c r="J12" s="14">
+      <c r="J12" s="5">
         <v>1.5384615384615399E-2</v>
       </c>
-      <c r="K12" s="14">
+      <c r="K12" s="5">
         <v>2.6373626373626401E-2</v>
       </c>
-      <c r="L12" s="14">
-        <v>0</v>
-      </c>
-      <c r="M12" s="14">
-        <v>0</v>
-      </c>
-      <c r="N12" s="14">
+      <c r="L12" s="5">
+        <v>0</v>
+      </c>
+      <c r="M12" s="5">
+        <v>0</v>
+      </c>
+      <c r="N12" s="5">
         <v>0.634920634920635</v>
       </c>
-      <c r="O12" s="14">
+      <c r="O12" s="5">
         <v>0.120634920634921</v>
       </c>
-      <c r="P12" s="14">
+      <c r="P12" s="5">
         <v>8.2539682539682496E-2</v>
       </c>
-      <c r="Q12" s="14">
+      <c r="Q12" s="5">
         <v>5.0793650793650801E-2</v>
       </c>
-      <c r="R12" s="14">
+      <c r="R12" s="5">
         <v>1.58730158730159E-2</v>
       </c>
-      <c r="S12" s="14">
+      <c r="S12" s="5">
         <v>3.8095238095238099E-2</v>
       </c>
-      <c r="T12" s="14">
+      <c r="T12" s="5">
         <v>6.3492063492063501E-3</v>
       </c>
-      <c r="U12" s="14">
+      <c r="U12" s="5">
         <v>5.0793650793650801E-2</v>
       </c>
-      <c r="V12" s="14">
-        <v>0</v>
-      </c>
-      <c r="W12" s="14">
-        <v>0</v>
-      </c>
-      <c r="X12" s="14">
+      <c r="V12" s="5">
+        <v>0</v>
+      </c>
+      <c r="W12" s="5">
+        <v>0</v>
+      </c>
+      <c r="X12" s="5">
         <v>0.7</v>
       </c>
-      <c r="Y12" s="14">
+      <c r="Y12" s="5">
         <v>0.1</v>
       </c>
-      <c r="Z12" s="14">
+      <c r="Z12" s="5">
         <v>8.5714285714285701E-2</v>
       </c>
-      <c r="AA12" s="14">
+      <c r="AA12" s="5">
         <v>1.4285714285714299E-2</v>
       </c>
-      <c r="AB12" s="14">
-        <v>0</v>
-      </c>
-      <c r="AC12" s="14">
+      <c r="AB12" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC12" s="5">
         <v>1.4285714285714299E-2</v>
       </c>
-      <c r="AD12" s="14">
-        <v>0</v>
-      </c>
-      <c r="AE12" s="14">
+      <c r="AD12" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE12" s="5">
         <v>8.5714285714285701E-2</v>
       </c>
-      <c r="AF12" s="14">
-        <v>0</v>
-      </c>
-      <c r="AG12" s="14">
-        <v>0</v>
-      </c>
-      <c r="AH12" s="14">
+      <c r="AF12" s="5">
+        <v>0</v>
+      </c>
+      <c r="AG12" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH12" s="5">
         <v>1</v>
       </c>
-      <c r="AI12" s="14">
-        <v>0</v>
-      </c>
-      <c r="AJ12" s="14">
-        <v>0</v>
-      </c>
-      <c r="AK12" s="14">
-        <v>0</v>
-      </c>
-      <c r="AL12" s="14">
-        <v>0</v>
-      </c>
-      <c r="AM12" s="14">
-        <v>0</v>
-      </c>
-      <c r="AN12" s="14">
-        <v>0</v>
-      </c>
-      <c r="AO12" s="14">
-        <v>0</v>
-      </c>
-      <c r="AP12" s="14">
-        <v>0</v>
-      </c>
-      <c r="AQ12" s="14">
-        <v>0</v>
-      </c>
-      <c r="AR12" s="14">
+      <c r="AI12" s="5">
+        <v>0</v>
+      </c>
+      <c r="AJ12" s="5">
+        <v>0</v>
+      </c>
+      <c r="AK12" s="5">
+        <v>0</v>
+      </c>
+      <c r="AL12" s="5">
+        <v>0</v>
+      </c>
+      <c r="AM12" s="5">
+        <v>0</v>
+      </c>
+      <c r="AN12" s="5">
+        <v>0</v>
+      </c>
+      <c r="AO12" s="5">
+        <v>0</v>
+      </c>
+      <c r="AP12" s="5">
+        <v>0</v>
+      </c>
+      <c r="AQ12" s="5">
+        <v>0</v>
+      </c>
+      <c r="AR12" s="5">
         <v>1</v>
       </c>
-      <c r="AS12" s="14">
-        <v>0</v>
-      </c>
-      <c r="AT12" s="14">
-        <v>0</v>
-      </c>
-      <c r="AU12" s="14">
-        <v>0</v>
-      </c>
-      <c r="AV12" s="14">
-        <v>0</v>
-      </c>
-      <c r="AW12" s="14">
-        <v>0</v>
-      </c>
-      <c r="AX12" s="14">
-        <v>0</v>
-      </c>
-      <c r="AY12" s="14">
-        <v>0</v>
-      </c>
-      <c r="AZ12" s="14">
-        <v>0</v>
-      </c>
-      <c r="BA12" s="14">
+      <c r="AS12" s="5">
+        <v>0</v>
+      </c>
+      <c r="AT12" s="5">
+        <v>0</v>
+      </c>
+      <c r="AU12" s="5">
+        <v>0</v>
+      </c>
+      <c r="AV12" s="5">
+        <v>0</v>
+      </c>
+      <c r="AW12" s="5">
+        <v>0</v>
+      </c>
+      <c r="AX12" s="5">
+        <v>0</v>
+      </c>
+      <c r="AY12" s="5">
+        <v>0</v>
+      </c>
+      <c r="AZ12" s="5">
+        <v>0</v>
+      </c>
+      <c r="BA12" s="5">
+        <v>0</v>
+      </c>
+      <c r="BB12" s="5">
+        <v>1</v>
+      </c>
+      <c r="BC12" s="5">
+        <v>0</v>
+      </c>
+      <c r="BD12" s="5">
+        <v>0</v>
+      </c>
+      <c r="BE12" s="5">
+        <v>0</v>
+      </c>
+      <c r="BF12" s="5">
+        <v>0</v>
+      </c>
+      <c r="BG12" s="5">
+        <v>0</v>
+      </c>
+      <c r="BH12" s="5">
+        <v>0</v>
+      </c>
+      <c r="BI12" s="5">
+        <v>0</v>
+      </c>
+      <c r="BJ12" s="5">
+        <v>0</v>
+      </c>
+      <c r="BK12" s="5">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
+    <mergeCell ref="BB1:BK1"/>
     <mergeCell ref="AH1:AQ1"/>
     <mergeCell ref="AR1:BA1"/>
     <mergeCell ref="A1:A2"/>
@@ -2661,6 +3013,7 @@
     <mergeCell ref="N1:W1"/>
     <mergeCell ref="X1:AG1"/>
   </mergeCells>
+  <phoneticPr fontId="4" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.47244094488188981" bottom="0.35433070866141736" header="0.23622047244094491" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="35" fitToHeight="0" pageOrder="overThenDown" orientation="landscape" r:id="rId1"/>
